--- a/02_DIA_inicio_2026_analisis_assets/rbd_9736_escuela-basica-bernardo-o-higgins_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9736_escuela-basica-bernardo-o-higgins_nt2_nucleos.xlsx
@@ -679,13 +679,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32298272-E058-46E3-AC81-F9EBD867499C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFB6A1CC-5F4B-4606-A85D-444EA20BFCD0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D70BFC2D-BD18-45A0-950B-947D8E7FB1BD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10E72F9E-3981-4114-9B38-D5217C2028E5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DC60736-ADC4-4D3B-BE9B-40A5186262B8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD56AC8D-86BB-4E7E-A61E-F16A1DBF104E}"/>
 </file>